--- a/data/Tesis_final/Mina_modelo/Produccion_base/zona_norte/1C/RED_GEN_BESS/elmo_data.xlsx
+++ b/data/Tesis_final/Mina_modelo/Produccion_base/zona_norte/1C/RED_GEN_BESS/elmo_data.xlsx
@@ -3349,7 +3349,7 @@
         <v>500</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -3376,7 +3376,7 @@
         <v>500</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3515,7 +3515,7 @@
         <v>1000</v>
       </c>
       <c r="I3" s="21" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
